--- a/MAJSushiConfig/ig/StructureDefinition-FRLMOrder.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-FRLMOrder.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMOrder</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMOrder</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:25:17+00:00</t>
+    <t>2026-09-07T11:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,8 +279,8 @@
     <t>FRLMOrder.orderPlacer[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMHealthProfessional
-https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMOrganisationhttps://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMPatient</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHealthProfessional
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMOrganisationhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPatient</t>
   </si>
   <si>
     <t>La personne/l'organisation à l'origine de la demande.</t>
@@ -290,7 +290,7 @@
   </si>
   <si>
     <t>CodeableConcept
-https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMConditionhttps://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMObservation</t>
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMConditionhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMObservation</t>
   </si>
   <si>
     <t>Motif de la demande.</t>
@@ -608,7 +608,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="145.0390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="133.65234375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/MAJSushiConfig/ig/StructureDefinition-FRLMOrder.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-FRLMOrder.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T11:26:50+00:00</t>
+    <t>2026-09-07T11:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
